--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_120_R12.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_120_R12.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9423</v>
+        <v>4.2454</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7224</v>
+        <v>3.9583</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2199</v>
+        <v>0.2871</v>
       </c>
       <c r="G2" t="n">
         <v>4.7823</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7677</v>
+        <v>-1.4646</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4129</v>
+        <v>0.6488</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.1807</v>
+        <v>-2.1135</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. HACKETT</t>
+          <t>C. EDWARDS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2135</v>
+        <v>3.443</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5451</v>
+        <v>4.309</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3316</v>
+        <v>-0.866</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8646</v>
+        <v>5.5804</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1982</v>
+        <v>-0.3516</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6664</v>
+        <v>5.932</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3354</v>
+        <v>8.0786</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.4068</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2514</v>
+        <v>7.6718</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5292</v>
+        <v>-2.4982</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1141</v>
+        <v>-0.7584</v>
       </c>
       <c r="O3" t="n">
-        <v>0.415</v>
+        <v>-1.7398</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1892</v>
+        <v>0.2054</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2097</v>
+        <v>-0.2671</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0205</v>
+        <v>0.4725</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5361</v>
+        <v>-1.1829</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-1.1829</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. EDWARDS</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6538</v>
+        <v>2.4001</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6878</v>
+        <v>2.7649</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.034</v>
+        <v>-0.3649</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5804</v>
+        <v>2.0302</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3516</v>
+        <v>0.0961</v>
       </c>
       <c r="I4" t="n">
-        <v>5.932</v>
+        <v>1.9341</v>
       </c>
       <c r="J4" t="n">
-        <v>8.0786</v>
+        <v>1.1972</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4068</v>
+        <v>-0.1646</v>
       </c>
       <c r="L4" t="n">
-        <v>7.6718</v>
+        <v>1.3618</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.4982</v>
+        <v>0.8329</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7584</v>
+        <v>0.2606</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.7398</v>
+        <v>0.5723</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5838</v>
+        <v>-0.2743</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8883</v>
+        <v>0.4955</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3044</v>
+        <v>-0.7699</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.1829</v>
+        <v>-0.2836</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.1829</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>D. HACKETT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6353</v>
+        <v>2.1019</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7649</v>
+        <v>2.6015</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1297</v>
+        <v>-0.4996</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0302</v>
+        <v>1.8646</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0961</v>
+        <v>0.1982</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9341</v>
+        <v>1.6664</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1972</v>
+        <v>1.3354</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1646</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3618</v>
+        <v>1.2514</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8329</v>
+        <v>0.5292</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2606</v>
+        <v>0.1141</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5723</v>
+        <v>0.415</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0391</v>
+        <v>0.0775</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4955</v>
+        <v>1.2661</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5346</v>
+        <v>-1.1885</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2836</v>
+        <v>-0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3558</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0683</v>
+        <v>1.8968</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9427</v>
+        <v>2.5024</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8744</v>
+        <v>-0.6056</v>
       </c>
       <c r="G6" t="n">
         <v>3.7368</v>
@@ -922,13 +922,13 @@
         <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2046</v>
+        <v>-1.3761</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5272</v>
+        <v>0.0868</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.7317</v>
+        <v>-1.4629</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8757</v>
+        <v>1.4023</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5991</v>
+        <v>0.3946</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2766</v>
+        <v>1.0077</v>
       </c>
       <c r="G7" t="n">
         <v>1.4602</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6423</v>
+        <v>0.1689</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6097</v>
+        <v>0.4052</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0325</v>
+        <v>-0.2363</v>
       </c>
       <c r="V7" t="n">
         <v>1.8608</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7459</v>
+        <v>-0.3994</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2596</v>
+        <v>0.316</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5137</v>
+        <v>-0.7154</v>
       </c>
       <c r="G8" t="n">
         <v>1.0326</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.9452</v>
+        <v>0.8</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5727</v>
+        <v>0.6291</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3725</v>
+        <v>0.1709</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.323</v>
+        <v>-0.8341</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8363</v>
+        <v>-0.2465</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4867</v>
+        <v>-0.5876</v>
       </c>
       <c r="G9" t="n">
         <v>0.137</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.4421</v>
+        <v>-1.9531</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4481</v>
+        <v>0.1417</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.994</v>
+        <v>-2.0948</v>
       </c>
       <c r="V9" t="n">
         <v>1.214</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. DIARRA</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2099</v>
+        <v>-1.4417</v>
       </c>
       <c r="E10" t="n">
-        <v>0.971</v>
+        <v>-1.1915</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1809</v>
+        <v>-0.2502</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2417</v>
+        <v>0.0876</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6231</v>
+        <v>-0.8726</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3814</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9707</v>
+        <v>1.0098</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8234</v>
+        <v>-0.1141</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1472</v>
+        <v>1.124</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.729</v>
+        <v>-0.9222</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2004</v>
+        <v>-0.7584</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5286</v>
+        <v>-0.1638</v>
       </c>
       <c r="P10" t="n">
-        <v>0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6808999999999999</v>
+        <v>0.7027</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1415</v>
+        <v>0.1182</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5395</v>
+        <v>0.5845</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0026</v>
+        <v>-1.0722</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>A. DIARRA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2652</v>
+        <v>-1.6037</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0486</v>
+        <v>1.4428</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2166</v>
+        <v>-3.0465</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0876</v>
+        <v>0.2417</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8726</v>
+        <v>0.6231</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9602000000000001</v>
+        <v>-0.3814</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0098</v>
+        <v>0.9707</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1141</v>
+        <v>0.8234</v>
       </c>
       <c r="L11" t="n">
-        <v>1.124</v>
+        <v>0.1472</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9222</v>
+        <v>-0.729</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7584</v>
+        <v>-0.2004</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1638</v>
+        <v>-0.5286</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1208</v>
+        <v>-0.0747</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7389</v>
+        <v>0.3304</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6181</v>
+        <v>-0.405</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>-2.0026</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7099</v>
+        <v>-1.837</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1125</v>
+        <v>0.6157</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8224</v>
+        <v>-2.4527</v>
       </c>
       <c r="G12" t="n">
         <v>1.6698</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.1477</v>
+        <v>-1.2748</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8962</v>
+        <v>-0.393</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2516</v>
+        <v>-0.8819</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.626799999999996</v>
+        <v>9.3736</v>
       </c>
       <c r="E13" t="n">
-        <v>16.7202</v>
+        <v>17.4672</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.093499999999999</v>
+        <v>-8.0937</v>
       </c>
       <c r="G13" t="n">
         <v>22.6232</v>
@@ -1444,7 +1444,7 @@
         <v>24.337</v>
       </c>
       <c r="K13" t="n">
-        <v>9.566199999999998</v>
+        <v>9.5662</v>
       </c>
       <c r="L13" t="n">
         <v>14.7711</v>
@@ -1456,7 +1456,7 @@
         <v>-1.6488</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.06539999999999979</v>
+        <v>-0.06539999999999974</v>
       </c>
       <c r="P13" t="n">
         <v>-4.639199999999999</v>
@@ -1468,13 +1468,13 @@
         <v>10.438</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.209999999999999</v>
+        <v>-4.4631</v>
       </c>
       <c r="T13" t="n">
-        <v>2.714700000000001</v>
+        <v>3.4617</v>
       </c>
       <c r="U13" t="n">
-        <v>-7.9251</v>
+        <v>-7.9249</v>
       </c>
       <c r="V13" t="n">
         <v>-4.147</v>
@@ -1483,7 +1483,7 @@
         <v>4.7453</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.892299999999999</v>
+        <v>-8.892300000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4666</v>
+        <v>4.9891</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5903</v>
+        <v>4.18</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8763</v>
+        <v>0.8091</v>
       </c>
       <c r="G14" t="n">
         <v>0.1014</v>
@@ -1546,13 +1546,13 @@
         <v>2.7834</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5096000000000001</v>
+        <v>1.0321</v>
       </c>
       <c r="T14" t="n">
-        <v>1.223</v>
+        <v>1.8128</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7134</v>
+        <v>-0.7806</v>
       </c>
       <c r="V14" t="n">
         <v>1.0722</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.647</v>
+        <v>3.8379</v>
       </c>
       <c r="E15" t="n">
         <v>3.6085</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0385</v>
+        <v>0.2294</v>
       </c>
       <c r="G15" t="n">
         <v>-2.6339</v>
@@ -1624,13 +1624,13 @@
         <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1391</v>
+        <v>1.33</v>
       </c>
       <c r="T15" t="n">
         <v>2.0014</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8623</v>
+        <v>-0.6715</v>
       </c>
       <c r="V15" t="n">
         <v>2.8223</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8391999999999999</v>
+        <v>1.2438</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8631</v>
+        <v>3.3349</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0238</v>
+        <v>-2.091</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1365</v>
@@ -1702,13 +1702,13 @@
         <v>2.7834</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2768</v>
+        <v>0.1278</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2873</v>
+        <v>0.7591</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5641</v>
+        <v>-0.6313</v>
       </c>
       <c r="V16" t="n">
         <v>0.7886</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. LAVI</t>
+          <t>J. DOWTIN JR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1244</v>
+        <v>-0.2461</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2838</v>
+        <v>2.5247</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1593</v>
+        <v>-2.7708</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.3763</v>
+        <v>-2.7576</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2784</v>
+        <v>0.5952</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0979</v>
+        <v>-3.3528</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.07099999999999999</v>
+        <v>1.8846</v>
       </c>
       <c r="K17" t="n">
-        <v>0.605</v>
+        <v>1.6574</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.2272</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3053</v>
+        <v>-4.6422</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8834</v>
+        <v>-1.0622</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.422</v>
+        <v>-3.58</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4639</v>
+        <v>2.3195</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>2.3195</v>
       </c>
       <c r="S17" t="n">
-        <v>2.681</v>
+        <v>-0.2023</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1587</v>
+        <v>-0.4321</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5223</v>
+        <v>0.2298</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2836</v>
+        <v>0.3943</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3558</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. OMORUYI</t>
+          <t>G. LAVI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4327</v>
+        <v>-0.6841</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6478</v>
+        <v>1.5761</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0805</v>
+        <v>-2.2602</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.771</v>
+        <v>-2.3763</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1056</v>
+        <v>-0.2784</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3346</v>
+        <v>-2.0979</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6959</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7695</v>
+        <v>0.605</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0736</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0751</v>
+        <v>-2.3053</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3361</v>
+        <v>-0.8834</v>
       </c>
       <c r="O18" t="n">
-        <v>0.261</v>
+        <v>-1.422</v>
       </c>
       <c r="P18" t="n">
         <v>-0.4639</v>
@@ -1858,19 +1858,19 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8022</v>
+        <v>1.8725</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4312</v>
+        <v>1.451</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6291</v>
+        <v>0.4215</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>1.3558</v>
       </c>
       <c r="X18" t="n">
         <v>-1.0722</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. DOWTIN JR</t>
+          <t>C. OMORUYI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1948</v>
+        <v>-1.2584</v>
       </c>
       <c r="E19" t="n">
-        <v>1.935</v>
+        <v>-0.1779</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.1297</v>
+        <v>-1.0805</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.7576</v>
+        <v>-0.771</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5952</v>
+        <v>-1.1056</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.3528</v>
+        <v>0.3346</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8846</v>
+        <v>-0.6959</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6574</v>
+        <v>-0.7695</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2272</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.6422</v>
+        <v>-0.0751</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0622</v>
+        <v>-0.3361</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.58</v>
+        <v>0.261</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3195</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.151</v>
+        <v>-0.0235</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0218</v>
+        <v>0.6056</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1291</v>
+        <v>-0.6291</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2855</v>
+        <v>-1.9595</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5883</v>
+        <v>0.8242</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8738</v>
+        <v>-2.7837</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6271</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4112</v>
+        <v>0.7371</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2873</v>
+        <v>0.5232</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1239</v>
+        <v>0.2139</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1418</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3134</v>
+        <v>-3.1454</v>
       </c>
       <c r="E21" t="n">
         <v>-1.6188</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6946</v>
+        <v>-1.5265</v>
       </c>
       <c r="G21" t="n">
         <v>-3.3666</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2851</v>
+        <v>0.4531</v>
       </c>
       <c r="T21" t="n">
         <v>0.6528</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3677</v>
+        <v>-0.1997</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4028</v>
+        <v>-4.8689</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7514</v>
+        <v>-2.3411</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6515</v>
+        <v>-2.5278</v>
       </c>
       <c r="G22" t="n">
         <v>-5.0303</v>
@@ -2170,13 +2170,13 @@
         <v>2.0876</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7718</v>
+        <v>0.3058</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6256</v>
+        <v>0.0358</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1463</v>
+        <v>0.27</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.075</v>
+        <v>-5.749</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.053</v>
+        <v>-3.8171</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.022</v>
+        <v>-1.932</v>
       </c>
       <c r="G23" t="n">
         <v>-4.0252</v>
@@ -2248,13 +2248,13 @@
         <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0378</v>
+        <v>0.3637</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2794</v>
+        <v>0.5153</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2416</v>
+        <v>-0.1516</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.627000000000001</v>
+        <v>-7.840599999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>8.093600000000002</v>
+        <v>8.093499999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.7204</v>
+        <v>-15.934</v>
       </c>
       <c r="G24" t="n">
         <v>-22.6231</v>
@@ -2305,7 +2305,7 @@
         <v>1.6488</v>
       </c>
       <c r="L24" t="n">
-        <v>0.06520000000000037</v>
+        <v>0.06519999999999948</v>
       </c>
       <c r="M24" t="n">
         <v>-24.3371</v>
@@ -2326,16 +2326,16 @@
         <v>15.077</v>
       </c>
       <c r="S24" t="n">
-        <v>5.21</v>
+        <v>5.9963</v>
       </c>
       <c r="T24" t="n">
-        <v>7.924900000000001</v>
+        <v>7.924899999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.7148</v>
+        <v>-1.9286</v>
       </c>
       <c r="V24" t="n">
-        <v>4.146999999999998</v>
+        <v>4.147</v>
       </c>
       <c r="W24" t="n">
         <v>8.892199999999999</v>
